--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -20,11 +20,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -126,21 +126,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,9 +150,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-10 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -656,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -671,10 +672,8 @@
           <t>DCF intrinsic value / share</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>4.45</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -689,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,10 +702,8 @@
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B10" s="8" t="n">
+        <v>0.712</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -729,57 +726,72 @@
           <t>value_score</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>dcf_margin</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -790,6 +802,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -797,7 +810,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -863,8 +875,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>0.04547999858856201</v>
+      <c r="B5" s="10" t="n">
+        <v>0.04963000297546387</v>
       </c>
     </row>
     <row r="6">
@@ -873,7 +885,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -883,7 +895,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -893,7 +905,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -903,7 +915,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -913,7 +925,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -923,7 +935,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <v>-0.0125</v>
       </c>
     </row>
@@ -933,7 +945,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -943,8 +955,8 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>-829000</v>
+      <c r="B13" s="13" t="n">
+        <v>682000</v>
       </c>
     </row>
     <row r="15">
@@ -953,7 +965,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -964,18 +976,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1022,23 +1034,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="17">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="17">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1049,23 +1061,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="18">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="18">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="18">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1076,23 +1088,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1103,7 +1115,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1114,7 +1126,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1125,18 +1137,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1161,8 +1173,8 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
-        <v>154000</v>
+      <c r="B32" s="13" t="n">
+        <v>148000</v>
       </c>
     </row>
     <row r="33">
@@ -1171,8 +1183,8 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>34733000</v>
+      <c r="B33" s="13" t="n">
+        <v>34173000</v>
       </c>
     </row>
     <row r="34">
@@ -1181,7 +1193,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1192,17 +1204,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>12404195.74468085</v>
+      <c r="B35" s="21" t="n">
+        <v>12298195.38461538</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1213,17 +1225,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
-        <v>2.82</v>
+      <c r="B37" s="23" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="24">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1243,158 +1255,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="26">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="26">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="26">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25">
+      <c r="A43" s="26">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25">
+      <c r="A44" s="26">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25">
+      <c r="A45" s="26">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="28">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25">
+      <c r="A46" s="26">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25">
+      <c r="A47" s="26">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1450,59 +1462,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>GROW</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>U.S. Global Investors, Inc.</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
-        <v>34979832</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>-0.01</v>
+      <c r="C5" s="31" t="n">
+        <v>31975308</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
@@ -1516,15 +1528,15 @@
           <t>Akso Health Group</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>1187563264</v>
-      </c>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n">
-        <v>-808.128</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>79.621</v>
+      <c r="C6" s="33" t="n">
+        <v>1053746176</v>
+      </c>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
+        <v>-669.479</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>78.818</v>
       </c>
     </row>
     <row r="7">
@@ -1538,15 +1550,15 @@
           <t>Binah Capital Group, Inc.</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
-        <v>26391908</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>17.444445</v>
-      </c>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n">
-        <v>0.321</v>
+      <c r="C7" s="33" t="n">
+        <v>18510244</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>7.7500005</v>
+      </c>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n">
+        <v>0.269</v>
       </c>
     </row>
     <row r="8">
@@ -1560,10 +1572,10 @@
           <t>DYCQ</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1576,13 +1588,13 @@
           <t>Equus Total Return, Inc.</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>17896924</v>
-      </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n">
-        <v>15.206</v>
+      <c r="C9" s="33" t="n">
+        <v>11452691</v>
+      </c>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n">
+        <v>10.694</v>
       </c>
     </row>
     <row r="10">
@@ -1596,13 +1608,13 @@
           <t>Investcorp Credit Management BD</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>17824104</v>
-      </c>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n">
-        <v>7.392</v>
+      <c r="C10" s="33" t="n">
+        <v>9295955</v>
+      </c>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n">
+        <v>7.022</v>
       </c>
     </row>
     <row r="11">
@@ -1616,15 +1628,15 @@
           <t>Kentucky First Federal Bancorp</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>37523172</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>27.294706</v>
-      </c>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="33" t="n">
-        <v>6.001</v>
+      <c r="C11" s="33" t="n">
+        <v>42212656</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n">
+        <v>6.556</v>
       </c>
     </row>
     <row r="12">
@@ -1638,12 +1650,12 @@
           <t xml:space="preserve">Principal Capital Appreciation </t>
         </is>
       </c>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="33" t="n">
-        <v>29.164345</v>
-      </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="34" t="n">
+        <v>25.352057</v>
+      </c>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1656,10 +1668,10 @@
           <t>Pearl Diver Credit Company Inc.</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1667,15 +1679,15 @@
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>MEDIAN(D6:D13)</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>MEDIAN(E6:E13)</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>MEDIAN(F6:F13)</f>
         <v/>
       </c>
@@ -1686,15 +1698,15 @@
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <f>AVERAGE(D6:D13)</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>AVERAGE(E6:E13)</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>AVERAGE(F6:F13)</f>
         <v/>
       </c>
@@ -1705,9 +1717,9 @@
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.6</v>
+        <v>2.6161</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.712</v>
+        <v>0.701</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04991999626159668</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>12298195.38461538</v>
+        <v>12298196.55211957</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>2.6</v>
+        <v>2.6161</v>
       </c>
     </row>
     <row r="38">
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>31975308</v>
+        <v>32173312</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.83</v>
+        <v>10.9</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>-0.22</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1053746176</v>
+        <v>1045179136</v>
       </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="34" t="n">
-        <v>-669.479</v>
+        <v>-643.175</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.818</v>
+        <v>75.721</v>
       </c>
     </row>
     <row r="7">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>18510244</v>
+        <v>19619152</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>7.7500005</v>
+        <v>8.214286</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>0.269</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>11452691</v>
+        <v>11368891</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>10.694</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="10">
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>9295955</v>
+        <v>9137198</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>7.022</v>
+        <v>7.032</v>
       </c>
     </row>
     <row r="11">
@@ -1632,11 +1632,11 @@
         <v>42212656</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>21.75</v>
+        <v>22.69565</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>6.556</v>
+        <v>6.461</v>
       </c>
     </row>
     <row r="12">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="34" t="n">
-        <v>25.352057</v>
+        <v>25.238255</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.6161</v>
+        <v>2.6246</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.701</v>
+        <v>0.695</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04991999626159668</v>
+        <v>0.0498799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>12298196.55211957</v>
+        <v>12298195.53455765</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>2.6161</v>
+        <v>2.6246</v>
       </c>
     </row>
     <row r="38">
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>32173312</v>
+        <v>32277844</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.9</v>
+        <v>10.94</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1045179136</v>
+        <v>1113715456</v>
       </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="34" t="n">
-        <v>-643.175</v>
+        <v>-685.2619999999999</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>75.721</v>
+        <v>80.676</v>
       </c>
     </row>
     <row r="7">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>19619152</v>
+        <v>18169042</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.214286</v>
+        <v>7.6071434</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="8">
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>11368891</v>
+        <v>10965253</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>10.246</v>
+        <v>9.938000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>9137198</v>
+        <v>10102730</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>7.032</v>
+        <v>7.079</v>
       </c>
     </row>
     <row r="11">
@@ -1632,7 +1632,7 @@
         <v>42212656</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>22.69565</v>
+        <v>21.75</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="34" t="n">
-        <v>25.238255</v>
+        <v>25.179287</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.6246</v>
+        <v>2.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.695</v>
+        <v>0.712</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.0498199987411499</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>12298195.53455765</v>
+        <v>12298195.38461538</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>2.6246</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>32277844</v>
+        <v>31975308</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>2.97</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1113715456</v>
+        <v>1088014336</v>
       </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="34" t="n">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>18169042</v>
+        <v>18595544</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>7.6071434</v>
+        <v>7.7857146</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>10965253</v>
+        <v>10508542</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n"/>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>10102730</v>
+        <v>10967235</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="34" t="n">
-        <v>25.179287</v>
+        <v>25.385859</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.6</v>
+        <v>2.6892</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.712</v>
+        <v>0.655</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0498199987411499</v>
+        <v>0.04993000030517578</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>12298195.38461538</v>
+        <v>12298195.74594675</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>2.6</v>
+        <v>2.6892</v>
       </c>
     </row>
     <row r="38">
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>31975308</v>
+        <v>33072308</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.83</v>
+        <v>11.21</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1088014336</v>
+        <v>1165117696</v>
       </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="34" t="n">
-        <v>-685.2619999999999</v>
+        <v>-669.479</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>80.676</v>
+        <v>78.818</v>
       </c>
     </row>
     <row r="7">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>18595544</v>
+        <v>18339642</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>7.7857146</v>
+        <v>7.6785717</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>10508542</v>
+        <v>8997346</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>9.938000000000001</v>
+        <v>9.032</v>
       </c>
     </row>
     <row r="10">
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>10967235</v>
+        <v>11117333</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>7.079</v>
+        <v>7.108</v>
       </c>
     </row>
     <row r="11">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>42212656</v>
+        <v>43025372</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>21.75</v>
+        <v>22.16875</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="34" t="n">
-        <v>25.385859</v>
+        <v>25.404638</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.6892</v>
+        <v>2.7064</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.655</v>
+        <v>0.641</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05015999794006348</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>12298195.74594675</v>
+        <v>12298195.38870825</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>2.6892</v>
+        <v>2.7064</v>
       </c>
     </row>
     <row r="38">
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>33072308</v>
+        <v>33283836</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.21</v>
+        <v>11.28</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1165117696</v>
+        <v>1070880256</v>
       </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="34" t="n">
-        <v>-669.479</v>
+        <v>-743.131</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.818</v>
+        <v>87.489</v>
       </c>
     </row>
     <row r="7">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>18339642</v>
+        <v>17914844</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>7.6785717</v>
+        <v>7.500714</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="8">
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>8997346</v>
+        <v>8938685</v>
       </c>
       <c r="D9" s="34" t="n"/>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>9.032</v>
+        <v>8.393000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>11117333</v>
+        <v>11257328</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>7.108</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="11">
@@ -1629,14 +1629,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>43025372</v>
+        <v>43505724</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>22.16875</v>
+        <v>22.41625</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>6.461</v>
+        <v>6.552</v>
       </c>
     </row>
     <row r="12">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="34" t="n">
-        <v>25.404638</v>
+        <v>25.419662</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>
